--- a/apps/web/test/fixtures/student-import.xlsx
+++ b/apps/web/test/fixtures/student-import.xlsx
@@ -137,7 +137,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>01000000001</t>
+          <t>01700000001</t>
         </is>
       </c>
     </row>
